--- a/aysha/FittingTests v2.xlsx
+++ b/aysha/FittingTests v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\transp02.cheng.auth.gr\d$\kkakosim\github\tamuq-chen-secarelab-receiver\aysha\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0744849C-1DE3-44AA-99A3-2F6260759C85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DF2B6A3-E6EA-4034-8FAC-C6F97C31F648}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,6 @@
     <sheet name="3D" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="164">
   <si>
     <t>A</t>
   </si>
@@ -515,6 +514,22 @@
   </si>
   <si>
     <t>trends appear the same, although a bit more abrupt</t>
+  </si>
+  <si>
+    <t>-&gt;50
+Mesh on domain 1 consists of 460315 elements. Minimum quality: 0.009841; average quality: 0.4185.</t>
+  </si>
+  <si>
+    <t>abs=0.85, I_factor=1.</t>
+  </si>
+  <si>
+    <t>-fully coupled</t>
+  </si>
+  <si>
+    <t>doesn't seem to affect anything</t>
+  </si>
+  <si>
+    <t>slightly higher</t>
   </si>
 </sst>
 </file>
@@ -568,7 +583,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -579,6 +594,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2213,14 +2231,32 @@
         <v>158</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A54" s="4">
         <v>52</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="H54" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="I54" s="4" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
         <v>53</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="I55" s="4" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
